--- a/파이썬/코딩교실 매크로/1.코딩교실준비/3.전산반배정/1.반이름/반이름.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/3.전산반배정/1.반이름/반이름.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\3.전산반배정\1.반이름\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCD7904-B48A-4092-A120-1E64FF9F1D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296B3662-8985-41D3-97F5-3B7B6791864D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34815" yWindow="1560" windowWidth="28770" windowHeight="15450" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39210" yWindow="2715" windowWidth="25320" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="출석부(월수)" sheetId="3" r:id="rId1"/>
@@ -3771,30 +3771,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3821,6 +3797,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4042,26 +4042,39 @@
   </sheetPr>
   <dimension ref="A1:L123"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="20" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="23" t="s">
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="24"/>
+      <c r="L1" s="30"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -4102,11 +4115,11 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25">
+      <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="31">
+      <c r="B3" s="20"/>
+      <c r="C3" s="23">
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -4138,9 +4151,9 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="32"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="24"/>
       <c r="D4" s="1" t="s">
         <v>52</v>
       </c>
@@ -4170,9 +4183,9 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="32"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="24"/>
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
@@ -4202,9 +4215,9 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="32"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="24"/>
       <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
@@ -4234,9 +4247,9 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="32"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="24"/>
       <c r="D7" s="1" t="s">
         <v>52</v>
       </c>
@@ -4266,9 +4279,9 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="33"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="8" t="s">
         <v>6</v>
       </c>
@@ -4298,11 +4311,11 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25">
+      <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="31">
+      <c r="B9" s="20"/>
+      <c r="C9" s="23">
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -4334,9 +4347,9 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="32"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="24"/>
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4366,9 +4379,9 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="32"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
@@ -4398,9 +4411,9 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="32"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="24"/>
       <c r="D12" s="1" t="s">
         <v>52</v>
       </c>
@@ -4430,9 +4443,9 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="32"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="24"/>
       <c r="D13" s="1" t="s">
         <v>52</v>
       </c>
@@ -4462,9 +4475,9 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="27"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="33"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="8" t="s">
         <v>52</v>
       </c>
@@ -4494,11 +4507,11 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="25">
+      <c r="A15" s="17">
         <v>3</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="31">
+      <c r="B15" s="20"/>
+      <c r="C15" s="23">
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -4530,9 +4543,9 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="32"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="24"/>
       <c r="D16" s="1" t="s">
         <v>52</v>
       </c>
@@ -4562,9 +4575,9 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="32"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="24"/>
       <c r="D17" s="1" t="s">
         <v>680</v>
       </c>
@@ -4594,9 +4607,9 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="32"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="24"/>
       <c r="D18" s="1" t="s">
         <v>52</v>
       </c>
@@ -4626,9 +4639,9 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="32"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="24"/>
       <c r="D19" s="1" t="s">
         <v>52</v>
       </c>
@@ -4658,9 +4671,9 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="33"/>
+      <c r="A20" s="19"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="25"/>
       <c r="D20" s="8" t="s">
         <v>52</v>
       </c>
@@ -4690,11 +4703,11 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="25">
-        <v>4</v>
-      </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="31">
+      <c r="A21" s="17">
+        <v>4</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="23">
         <v>6</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -4726,9 +4739,9 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="32"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="24"/>
       <c r="D22" s="1" t="s">
         <v>52</v>
       </c>
@@ -4758,9 +4771,9 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="32"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="24"/>
       <c r="D23" s="1" t="s">
         <v>6</v>
       </c>
@@ -4790,9 +4803,9 @@
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="32"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="24"/>
       <c r="D24" s="1" t="s">
         <v>6</v>
       </c>
@@ -4822,9 +4835,9 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="32"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="24"/>
       <c r="D25" s="1" t="s">
         <v>52</v>
       </c>
@@ -4854,9 +4867,9 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="27"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="33"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="25"/>
       <c r="D26" s="8" t="s">
         <v>6</v>
       </c>
@@ -4886,11 +4899,11 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25">
+      <c r="A27" s="17">
         <v>5</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="31">
+      <c r="B27" s="20"/>
+      <c r="C27" s="23">
         <v>6</v>
       </c>
       <c r="D27" s="11" t="s">
@@ -4916,9 +4929,9 @@
       <c r="L27" s="13"/>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="26"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="32"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="24"/>
       <c r="D28" s="1" t="s">
         <v>6</v>
       </c>
@@ -4948,9 +4961,9 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="26"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="32"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="24"/>
       <c r="D29" s="1" t="s">
         <v>6</v>
       </c>
@@ -4980,9 +4993,9 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="26"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="32"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="24"/>
       <c r="D30" s="1" t="s">
         <v>6</v>
       </c>
@@ -5012,9 +5025,9 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="32"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="24"/>
       <c r="D31" s="1" t="s">
         <v>6</v>
       </c>
@@ -5044,9 +5057,9 @@
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="26"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="32"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="24"/>
       <c r="D32" s="1" t="s">
         <v>52</v>
       </c>
@@ -5076,9 +5089,9 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="27"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="33"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="25"/>
       <c r="D33" s="8" t="s">
         <v>52</v>
       </c>
@@ -5108,11 +5121,11 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="25">
-        <v>6</v>
-      </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="31">
+      <c r="A34" s="17">
+        <v>6</v>
+      </c>
+      <c r="B34" s="20"/>
+      <c r="C34" s="23">
         <v>6</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -5144,9 +5157,9 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="32"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="24"/>
       <c r="D35" s="1" t="s">
         <v>6</v>
       </c>
@@ -5176,9 +5189,9 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="26"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="32"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="24"/>
       <c r="D36" s="1" t="s">
         <v>52</v>
       </c>
@@ -5208,9 +5221,9 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="26"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="32"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="24"/>
       <c r="D37" s="1" t="s">
         <v>6</v>
       </c>
@@ -5240,9 +5253,9 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="26"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="32"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="24"/>
       <c r="D38" s="1" t="s">
         <v>6</v>
       </c>
@@ -5272,9 +5285,9 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="27"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="33"/>
+      <c r="A39" s="19"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="25"/>
       <c r="D39" s="8" t="s">
         <v>6</v>
       </c>
@@ -5304,11 +5317,11 @@
       </c>
     </row>
     <row r="40" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="25">
-        <v>7</v>
-      </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="31">
+      <c r="A40" s="17">
+        <v>7</v>
+      </c>
+      <c r="B40" s="20"/>
+      <c r="C40" s="23">
         <v>6</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -5340,9 +5353,9 @@
       </c>
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="26"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="32"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="24"/>
       <c r="D41" s="1" t="s">
         <v>6</v>
       </c>
@@ -5372,9 +5385,9 @@
       </c>
     </row>
     <row r="42" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="26"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="32"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="24"/>
       <c r="D42" s="1" t="s">
         <v>6</v>
       </c>
@@ -5404,9 +5417,9 @@
       </c>
     </row>
     <row r="43" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="26"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="32"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="24"/>
       <c r="D43" s="1" t="s">
         <v>52</v>
       </c>
@@ -5436,9 +5449,9 @@
       </c>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="26"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="32"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="24"/>
       <c r="D44" s="1" t="s">
         <v>52</v>
       </c>
@@ -5468,9 +5481,9 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="33"/>
+      <c r="A45" s="19"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="25"/>
       <c r="D45" s="8" t="s">
         <v>52</v>
       </c>
@@ -5500,11 +5513,11 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="25">
+      <c r="A46" s="17">
         <v>8</v>
       </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="31">
+      <c r="B46" s="20"/>
+      <c r="C46" s="23">
         <v>6</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -5536,9 +5549,9 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="26"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="32"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="24"/>
       <c r="D47" s="1" t="s">
         <v>52</v>
       </c>
@@ -5568,9 +5581,9 @@
       </c>
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="26"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="32"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="24"/>
       <c r="D48" s="1" t="s">
         <v>6</v>
       </c>
@@ -5600,9 +5613,9 @@
       </c>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="26"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="32"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="24"/>
       <c r="D49" s="1" t="s">
         <v>6</v>
       </c>
@@ -5632,9 +5645,9 @@
       </c>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="26"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="32"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="24"/>
       <c r="D50" s="1" t="s">
         <v>6</v>
       </c>
@@ -5664,9 +5677,9 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="33"/>
+      <c r="A51" s="19"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="25"/>
       <c r="D51" s="8" t="s">
         <v>6</v>
       </c>
@@ -5696,11 +5709,11 @@
       </c>
     </row>
     <row r="52" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="25">
+      <c r="A52" s="17">
         <v>9</v>
       </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="31">
+      <c r="B52" s="20"/>
+      <c r="C52" s="23">
         <v>6</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -5732,9 +5745,9 @@
       </c>
     </row>
     <row r="53" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="26"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="32"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="24"/>
       <c r="D53" s="1" t="s">
         <v>6</v>
       </c>
@@ -5764,9 +5777,9 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="26"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="32"/>
+      <c r="A54" s="18"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="24"/>
       <c r="D54" s="1" t="s">
         <v>52</v>
       </c>
@@ -5796,9 +5809,9 @@
       </c>
     </row>
     <row r="55" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="26"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="32"/>
+      <c r="A55" s="18"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="24"/>
       <c r="D55" s="1" t="s">
         <v>52</v>
       </c>
@@ -5828,9 +5841,9 @@
       </c>
     </row>
     <row r="56" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="26"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="32"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="24"/>
       <c r="D56" s="1" t="s">
         <v>6</v>
       </c>
@@ -5860,9 +5873,9 @@
       </c>
     </row>
     <row r="57" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="27"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="33"/>
+      <c r="A57" s="19"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="25"/>
       <c r="D57" s="8" t="s">
         <v>6</v>
       </c>
@@ -5892,11 +5905,11 @@
       </c>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="25">
+      <c r="A58" s="17">
         <v>10</v>
       </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="31">
+      <c r="B58" s="20"/>
+      <c r="C58" s="23">
         <v>6</v>
       </c>
       <c r="D58" s="1" t="s">
@@ -5928,9 +5941,9 @@
       </c>
     </row>
     <row r="59" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="26"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="32"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="24"/>
       <c r="D59" s="1" t="s">
         <v>6</v>
       </c>
@@ -5960,9 +5973,9 @@
       </c>
     </row>
     <row r="60" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="26"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="32"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="24"/>
       <c r="D60" s="1" t="s">
         <v>52</v>
       </c>
@@ -5992,9 +6005,9 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="26"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="32"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="24"/>
       <c r="D61" s="1" t="s">
         <v>6</v>
       </c>
@@ -6024,9 +6037,9 @@
       </c>
     </row>
     <row r="62" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="26"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="32"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="24"/>
       <c r="D62" s="1" t="s">
         <v>6</v>
       </c>
@@ -6056,9 +6069,9 @@
       </c>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="27"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="33"/>
+      <c r="A63" s="19"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="25"/>
       <c r="D63" s="8" t="s">
         <v>6</v>
       </c>
@@ -6088,11 +6101,11 @@
       </c>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="25">
+      <c r="A64" s="17">
         <v>11</v>
       </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="31">
+      <c r="B64" s="20"/>
+      <c r="C64" s="23">
         <v>6</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -6124,9 +6137,9 @@
       </c>
     </row>
     <row r="65" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="26"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="32"/>
+      <c r="A65" s="18"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="24"/>
       <c r="D65" s="1" t="s">
         <v>52</v>
       </c>
@@ -6156,9 +6169,9 @@
       </c>
     </row>
     <row r="66" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="26"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="32"/>
+      <c r="A66" s="18"/>
+      <c r="B66" s="21"/>
+      <c r="C66" s="24"/>
       <c r="D66" s="1" t="s">
         <v>52</v>
       </c>
@@ -6188,9 +6201,9 @@
       </c>
     </row>
     <row r="67" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="26"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="32"/>
+      <c r="A67" s="18"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="24"/>
       <c r="D67" s="1" t="s">
         <v>6</v>
       </c>
@@ -6220,9 +6233,9 @@
       </c>
     </row>
     <row r="68" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="26"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="32"/>
+      <c r="A68" s="18"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="24"/>
       <c r="D68" s="1" t="s">
         <v>6</v>
       </c>
@@ -6252,9 +6265,9 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="27"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="33"/>
+      <c r="A69" s="19"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="25"/>
       <c r="D69" s="8" t="s">
         <v>6</v>
       </c>
@@ -6284,11 +6297,11 @@
       </c>
     </row>
     <row r="70" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="25">
+      <c r="A70" s="17">
         <v>12</v>
       </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="31">
+      <c r="B70" s="20"/>
+      <c r="C70" s="23">
         <v>6</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -6320,9 +6333,9 @@
       </c>
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="26"/>
-      <c r="B71" s="29"/>
-      <c r="C71" s="32"/>
+      <c r="A71" s="18"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="24"/>
       <c r="D71" s="1" t="s">
         <v>52</v>
       </c>
@@ -6352,9 +6365,9 @@
       </c>
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="26"/>
-      <c r="B72" s="29"/>
-      <c r="C72" s="32"/>
+      <c r="A72" s="18"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="24"/>
       <c r="D72" s="1" t="s">
         <v>6</v>
       </c>
@@ -6384,9 +6397,9 @@
       </c>
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="26"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="32"/>
+      <c r="A73" s="18"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="24"/>
       <c r="D73" s="1" t="s">
         <v>51</v>
       </c>
@@ -6416,9 +6429,9 @@
       </c>
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="26"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="32"/>
+      <c r="A74" s="18"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="24"/>
       <c r="D74" s="1" t="s">
         <v>6</v>
       </c>
@@ -6448,9 +6461,9 @@
       </c>
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="27"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="33"/>
+      <c r="A75" s="19"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="25"/>
       <c r="D75" s="8" t="s">
         <v>6</v>
       </c>
@@ -6480,11 +6493,11 @@
       </c>
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="25">
+      <c r="A76" s="17">
         <v>13</v>
       </c>
-      <c r="B76" s="28"/>
-      <c r="C76" s="31">
+      <c r="B76" s="20"/>
+      <c r="C76" s="23">
         <v>6</v>
       </c>
       <c r="D76" s="1" t="s">
@@ -6516,9 +6529,9 @@
       </c>
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="26"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="32"/>
+      <c r="A77" s="18"/>
+      <c r="B77" s="21"/>
+      <c r="C77" s="24"/>
       <c r="D77" s="1" t="s">
         <v>52</v>
       </c>
@@ -6548,9 +6561,9 @@
       </c>
     </row>
     <row r="78" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="26"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="32"/>
+      <c r="A78" s="18"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="24"/>
       <c r="D78" s="1" t="s">
         <v>6</v>
       </c>
@@ -6580,9 +6593,9 @@
       </c>
     </row>
     <row r="79" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="26"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="32"/>
+      <c r="A79" s="18"/>
+      <c r="B79" s="21"/>
+      <c r="C79" s="24"/>
       <c r="D79" s="1" t="s">
         <v>52</v>
       </c>
@@ -6612,9 +6625,9 @@
       </c>
     </row>
     <row r="80" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="26"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="32"/>
+      <c r="A80" s="18"/>
+      <c r="B80" s="21"/>
+      <c r="C80" s="24"/>
       <c r="D80" s="1" t="s">
         <v>52</v>
       </c>
@@ -6644,9 +6657,9 @@
       </c>
     </row>
     <row r="81" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="27"/>
-      <c r="B81" s="30"/>
-      <c r="C81" s="33"/>
+      <c r="A81" s="19"/>
+      <c r="B81" s="22"/>
+      <c r="C81" s="25"/>
       <c r="D81" s="8" t="s">
         <v>52</v>
       </c>
@@ -6676,11 +6689,11 @@
       </c>
     </row>
     <row r="82" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="25">
+      <c r="A82" s="17">
         <v>14</v>
       </c>
-      <c r="B82" s="28"/>
-      <c r="C82" s="31">
+      <c r="B82" s="20"/>
+      <c r="C82" s="23">
         <v>6</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -6712,9 +6725,9 @@
       </c>
     </row>
     <row r="83" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="26"/>
-      <c r="B83" s="29"/>
-      <c r="C83" s="32"/>
+      <c r="A83" s="18"/>
+      <c r="B83" s="21"/>
+      <c r="C83" s="24"/>
       <c r="D83" s="1" t="s">
         <v>6</v>
       </c>
@@ -6744,9 +6757,9 @@
       </c>
     </row>
     <row r="84" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="26"/>
-      <c r="B84" s="29"/>
-      <c r="C84" s="32"/>
+      <c r="A84" s="18"/>
+      <c r="B84" s="21"/>
+      <c r="C84" s="24"/>
       <c r="D84" s="1" t="s">
         <v>6</v>
       </c>
@@ -6776,9 +6789,9 @@
       </c>
     </row>
     <row r="85" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="26"/>
-      <c r="B85" s="29"/>
-      <c r="C85" s="32"/>
+      <c r="A85" s="18"/>
+      <c r="B85" s="21"/>
+      <c r="C85" s="24"/>
       <c r="D85" s="1" t="s">
         <v>52</v>
       </c>
@@ -6808,9 +6821,9 @@
       </c>
     </row>
     <row r="86" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="26"/>
-      <c r="B86" s="29"/>
-      <c r="C86" s="32"/>
+      <c r="A86" s="18"/>
+      <c r="B86" s="21"/>
+      <c r="C86" s="24"/>
       <c r="D86" s="1" t="s">
         <v>52</v>
       </c>
@@ -6840,9 +6853,9 @@
       </c>
     </row>
     <row r="87" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="27"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="33"/>
+      <c r="A87" s="19"/>
+      <c r="B87" s="22"/>
+      <c r="C87" s="25"/>
       <c r="D87" s="8" t="s">
         <v>52</v>
       </c>
@@ -6872,11 +6885,11 @@
       </c>
     </row>
     <row r="88" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="25">
+      <c r="A88" s="17">
         <v>15</v>
       </c>
-      <c r="B88" s="28"/>
-      <c r="C88" s="31">
+      <c r="B88" s="20"/>
+      <c r="C88" s="23">
         <v>6</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -6908,9 +6921,9 @@
       </c>
     </row>
     <row r="89" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="26"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="32"/>
+      <c r="A89" s="18"/>
+      <c r="B89" s="21"/>
+      <c r="C89" s="24"/>
       <c r="D89" s="1" t="s">
         <v>51</v>
       </c>
@@ -6940,9 +6953,9 @@
       </c>
     </row>
     <row r="90" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="26"/>
-      <c r="B90" s="29"/>
-      <c r="C90" s="32"/>
+      <c r="A90" s="18"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="24"/>
       <c r="D90" s="1" t="s">
         <v>6</v>
       </c>
@@ -6972,9 +6985,9 @@
       </c>
     </row>
     <row r="91" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="26"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="32"/>
+      <c r="A91" s="18"/>
+      <c r="B91" s="21"/>
+      <c r="C91" s="24"/>
       <c r="D91" s="1" t="s">
         <v>6</v>
       </c>
@@ -7004,9 +7017,9 @@
       </c>
     </row>
     <row r="92" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="26"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="32"/>
+      <c r="A92" s="18"/>
+      <c r="B92" s="21"/>
+      <c r="C92" s="24"/>
       <c r="D92" s="1" t="s">
         <v>52</v>
       </c>
@@ -7036,9 +7049,9 @@
       </c>
     </row>
     <row r="93" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="27"/>
-      <c r="B93" s="30"/>
-      <c r="C93" s="33"/>
+      <c r="A93" s="19"/>
+      <c r="B93" s="22"/>
+      <c r="C93" s="25"/>
       <c r="D93" s="8" t="s">
         <v>6</v>
       </c>
@@ -7068,11 +7081,11 @@
       </c>
     </row>
     <row r="94" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="25">
+      <c r="A94" s="17">
         <v>16</v>
       </c>
-      <c r="B94" s="28"/>
-      <c r="C94" s="31">
+      <c r="B94" s="20"/>
+      <c r="C94" s="23">
         <v>6</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -7104,9 +7117,9 @@
       </c>
     </row>
     <row r="95" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="26"/>
-      <c r="B95" s="29"/>
-      <c r="C95" s="32"/>
+      <c r="A95" s="18"/>
+      <c r="B95" s="21"/>
+      <c r="C95" s="24"/>
       <c r="D95" s="1" t="s">
         <v>51</v>
       </c>
@@ -7136,9 +7149,9 @@
       </c>
     </row>
     <row r="96" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="26"/>
-      <c r="B96" s="29"/>
-      <c r="C96" s="32"/>
+      <c r="A96" s="18"/>
+      <c r="B96" s="21"/>
+      <c r="C96" s="24"/>
       <c r="D96" s="1" t="s">
         <v>52</v>
       </c>
@@ -7168,9 +7181,9 @@
       </c>
     </row>
     <row r="97" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="26"/>
-      <c r="B97" s="29"/>
-      <c r="C97" s="32"/>
+      <c r="A97" s="18"/>
+      <c r="B97" s="21"/>
+      <c r="C97" s="24"/>
       <c r="D97" s="1" t="s">
         <v>6</v>
       </c>
@@ -7200,9 +7213,9 @@
       </c>
     </row>
     <row r="98" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="26"/>
-      <c r="B98" s="29"/>
-      <c r="C98" s="32"/>
+      <c r="A98" s="18"/>
+      <c r="B98" s="21"/>
+      <c r="C98" s="24"/>
       <c r="D98" s="1" t="s">
         <v>51</v>
       </c>
@@ -7232,9 +7245,9 @@
       </c>
     </row>
     <row r="99" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="27"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="33"/>
+      <c r="A99" s="19"/>
+      <c r="B99" s="22"/>
+      <c r="C99" s="25"/>
       <c r="D99" s="8" t="s">
         <v>52</v>
       </c>
@@ -7264,11 +7277,11 @@
       </c>
     </row>
     <row r="100" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="25">
+      <c r="A100" s="17">
         <v>17</v>
       </c>
-      <c r="B100" s="28"/>
-      <c r="C100" s="31">
+      <c r="B100" s="20"/>
+      <c r="C100" s="23">
         <v>6</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -7300,9 +7313,9 @@
       </c>
     </row>
     <row r="101" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="26"/>
-      <c r="B101" s="29"/>
-      <c r="C101" s="32"/>
+      <c r="A101" s="18"/>
+      <c r="B101" s="21"/>
+      <c r="C101" s="24"/>
       <c r="D101" s="1" t="s">
         <v>1041</v>
       </c>
@@ -7332,9 +7345,9 @@
       </c>
     </row>
     <row r="102" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="26"/>
-      <c r="B102" s="29"/>
-      <c r="C102" s="32"/>
+      <c r="A102" s="18"/>
+      <c r="B102" s="21"/>
+      <c r="C102" s="24"/>
       <c r="D102" s="1" t="s">
         <v>52</v>
       </c>
@@ -7364,9 +7377,9 @@
       </c>
     </row>
     <row r="103" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="26"/>
-      <c r="B103" s="29"/>
-      <c r="C103" s="32"/>
+      <c r="A103" s="18"/>
+      <c r="B103" s="21"/>
+      <c r="C103" s="24"/>
       <c r="D103" s="1" t="s">
         <v>1050</v>
       </c>
@@ -7396,9 +7409,9 @@
       </c>
     </row>
     <row r="104" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="26"/>
-      <c r="B104" s="29"/>
-      <c r="C104" s="32"/>
+      <c r="A104" s="18"/>
+      <c r="B104" s="21"/>
+      <c r="C104" s="24"/>
       <c r="D104" s="1" t="s">
         <v>52</v>
       </c>
@@ -7428,9 +7441,9 @@
       </c>
     </row>
     <row r="105" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="27"/>
-      <c r="B105" s="30"/>
-      <c r="C105" s="33"/>
+      <c r="A105" s="19"/>
+      <c r="B105" s="22"/>
+      <c r="C105" s="25"/>
       <c r="D105" s="8" t="s">
         <v>52</v>
       </c>
@@ -7460,11 +7473,11 @@
       </c>
     </row>
     <row r="106" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="25">
+      <c r="A106" s="17">
         <v>18</v>
       </c>
-      <c r="B106" s="28"/>
-      <c r="C106" s="31">
+      <c r="B106" s="20"/>
+      <c r="C106" s="23">
         <v>6</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -7496,9 +7509,9 @@
       </c>
     </row>
     <row r="107" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="26"/>
-      <c r="B107" s="29"/>
-      <c r="C107" s="32"/>
+      <c r="A107" s="18"/>
+      <c r="B107" s="21"/>
+      <c r="C107" s="24"/>
       <c r="D107" s="1" t="s">
         <v>52</v>
       </c>
@@ -7528,9 +7541,9 @@
       </c>
     </row>
     <row r="108" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="26"/>
-      <c r="B108" s="29"/>
-      <c r="C108" s="32"/>
+      <c r="A108" s="18"/>
+      <c r="B108" s="21"/>
+      <c r="C108" s="24"/>
       <c r="D108" s="1" t="s">
         <v>52</v>
       </c>
@@ -7560,9 +7573,9 @@
       </c>
     </row>
     <row r="109" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="26"/>
-      <c r="B109" s="29"/>
-      <c r="C109" s="32"/>
+      <c r="A109" s="18"/>
+      <c r="B109" s="21"/>
+      <c r="C109" s="24"/>
       <c r="D109" s="1" t="s">
         <v>52</v>
       </c>
@@ -7592,9 +7605,9 @@
       </c>
     </row>
     <row r="110" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="26"/>
-      <c r="B110" s="29"/>
-      <c r="C110" s="32"/>
+      <c r="A110" s="18"/>
+      <c r="B110" s="21"/>
+      <c r="C110" s="24"/>
       <c r="D110" s="1" t="s">
         <v>6</v>
       </c>
@@ -7624,9 +7637,9 @@
       </c>
     </row>
     <row r="111" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="27"/>
-      <c r="B111" s="30"/>
-      <c r="C111" s="33"/>
+      <c r="A111" s="19"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="25"/>
       <c r="D111" s="8" t="s">
         <v>52</v>
       </c>
@@ -7656,11 +7669,11 @@
       </c>
     </row>
     <row r="112" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="25">
+      <c r="A112" s="17">
         <v>19</v>
       </c>
-      <c r="B112" s="28"/>
-      <c r="C112" s="31">
+      <c r="B112" s="20"/>
+      <c r="C112" s="23">
         <v>6</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -7692,9 +7705,9 @@
       </c>
     </row>
     <row r="113" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="26"/>
-      <c r="B113" s="29"/>
-      <c r="C113" s="32"/>
+      <c r="A113" s="18"/>
+      <c r="B113" s="21"/>
+      <c r="C113" s="24"/>
       <c r="D113" s="1" t="s">
         <v>6</v>
       </c>
@@ -7724,9 +7737,9 @@
       </c>
     </row>
     <row r="114" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="26"/>
-      <c r="B114" s="29"/>
-      <c r="C114" s="32"/>
+      <c r="A114" s="18"/>
+      <c r="B114" s="21"/>
+      <c r="C114" s="24"/>
       <c r="D114" s="1" t="s">
         <v>6</v>
       </c>
@@ -7756,9 +7769,9 @@
       </c>
     </row>
     <row r="115" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="26"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="32"/>
+      <c r="A115" s="18"/>
+      <c r="B115" s="21"/>
+      <c r="C115" s="24"/>
       <c r="D115" s="1" t="s">
         <v>6</v>
       </c>
@@ -7788,9 +7801,9 @@
       </c>
     </row>
     <row r="116" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="26"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="32"/>
+      <c r="A116" s="18"/>
+      <c r="B116" s="21"/>
+      <c r="C116" s="24"/>
       <c r="D116" s="1" t="s">
         <v>52</v>
       </c>
@@ -7820,9 +7833,9 @@
       </c>
     </row>
     <row r="117" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="27"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="33"/>
+      <c r="A117" s="19"/>
+      <c r="B117" s="22"/>
+      <c r="C117" s="25"/>
       <c r="D117" s="8" t="s">
         <v>52</v>
       </c>
@@ -7852,11 +7865,11 @@
       </c>
     </row>
     <row r="118" spans="1:12" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="25">
+      <c r="A118" s="17">
         <v>20</v>
       </c>
-      <c r="B118" s="28"/>
-      <c r="C118" s="31">
+      <c r="B118" s="20"/>
+      <c r="C118" s="23">
         <v>5</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -7888,9 +7901,9 @@
       </c>
     </row>
     <row r="119" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="26"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="32"/>
+      <c r="A119" s="18"/>
+      <c r="B119" s="21"/>
+      <c r="C119" s="24"/>
       <c r="D119" s="1" t="s">
         <v>52</v>
       </c>
@@ -7920,9 +7933,9 @@
       </c>
     </row>
     <row r="120" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="26"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="32"/>
+      <c r="A120" s="18"/>
+      <c r="B120" s="21"/>
+      <c r="C120" s="24"/>
       <c r="D120" s="1" t="s">
         <v>680</v>
       </c>
@@ -7952,9 +7965,9 @@
       </c>
     </row>
     <row r="121" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="26"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="32"/>
+      <c r="A121" s="18"/>
+      <c r="B121" s="21"/>
+      <c r="C121" s="24"/>
       <c r="D121" s="1" t="s">
         <v>6</v>
       </c>
@@ -7984,9 +7997,9 @@
       </c>
     </row>
     <row r="122" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="27"/>
-      <c r="B122" s="30"/>
-      <c r="C122" s="33"/>
+      <c r="A122" s="19"/>
+      <c r="B122" s="22"/>
+      <c r="C122" s="25"/>
       <c r="D122" s="14" t="s">
         <v>6</v>
       </c>
@@ -8018,12 +8031,47 @@
     <row r="123" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="C34:C39"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="C40:C45"/>
+    <mergeCell ref="A112:A117"/>
+    <mergeCell ref="B112:B117"/>
+    <mergeCell ref="C112:C117"/>
+    <mergeCell ref="A118:A122"/>
+    <mergeCell ref="B118:B122"/>
+    <mergeCell ref="C118:C122"/>
+    <mergeCell ref="A100:A105"/>
+    <mergeCell ref="B100:B105"/>
+    <mergeCell ref="C100:C105"/>
+    <mergeCell ref="A106:A111"/>
+    <mergeCell ref="B106:B111"/>
+    <mergeCell ref="C106:C111"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="B88:B93"/>
+    <mergeCell ref="C88:C93"/>
+    <mergeCell ref="A94:A99"/>
+    <mergeCell ref="B94:B99"/>
+    <mergeCell ref="C94:C99"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="B76:B81"/>
+    <mergeCell ref="C76:C81"/>
+    <mergeCell ref="A82:A87"/>
+    <mergeCell ref="B82:B87"/>
+    <mergeCell ref="C82:C87"/>
+    <mergeCell ref="A64:A69"/>
+    <mergeCell ref="B64:B69"/>
+    <mergeCell ref="C64:C69"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="B70:B75"/>
+    <mergeCell ref="C70:C75"/>
+    <mergeCell ref="B52:B57"/>
+    <mergeCell ref="C52:C57"/>
+    <mergeCell ref="A58:A63"/>
+    <mergeCell ref="B58:B63"/>
+    <mergeCell ref="C58:C63"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="C3:C8"/>
     <mergeCell ref="A46:A51"/>
     <mergeCell ref="B46:B51"/>
     <mergeCell ref="C46:C51"/>
@@ -8037,50 +8085,15 @@
     <mergeCell ref="A21:A26"/>
     <mergeCell ref="B21:B26"/>
     <mergeCell ref="C21:C26"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="B3:B8"/>
-    <mergeCell ref="C3:C8"/>
     <mergeCell ref="A27:A33"/>
     <mergeCell ref="B27:B33"/>
     <mergeCell ref="C27:C33"/>
-    <mergeCell ref="B52:B57"/>
-    <mergeCell ref="C52:C57"/>
-    <mergeCell ref="A58:A63"/>
-    <mergeCell ref="B58:B63"/>
-    <mergeCell ref="C58:C63"/>
-    <mergeCell ref="A64:A69"/>
-    <mergeCell ref="B64:B69"/>
-    <mergeCell ref="C64:C69"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="B70:B75"/>
-    <mergeCell ref="C70:C75"/>
-    <mergeCell ref="A76:A81"/>
-    <mergeCell ref="B76:B81"/>
-    <mergeCell ref="C76:C81"/>
-    <mergeCell ref="A82:A87"/>
-    <mergeCell ref="B82:B87"/>
-    <mergeCell ref="C82:C87"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="B88:B93"/>
-    <mergeCell ref="C88:C93"/>
-    <mergeCell ref="A94:A99"/>
-    <mergeCell ref="B94:B99"/>
-    <mergeCell ref="C94:C99"/>
-    <mergeCell ref="A100:A105"/>
-    <mergeCell ref="B100:B105"/>
-    <mergeCell ref="C100:C105"/>
-    <mergeCell ref="A106:A111"/>
-    <mergeCell ref="B106:B111"/>
-    <mergeCell ref="C106:C111"/>
-    <mergeCell ref="A112:A117"/>
-    <mergeCell ref="B112:B117"/>
-    <mergeCell ref="C112:C117"/>
-    <mergeCell ref="A118:A122"/>
-    <mergeCell ref="B118:B122"/>
-    <mergeCell ref="C118:C122"/>
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="C34:C39"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="C40:C45"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
